--- a/artfynd/A 25839-2025 artfynd.xlsx
+++ b/artfynd/A 25839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851102</v>
       </c>
       <c r="B2" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129851150</v>
       </c>
       <c r="B3" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129851149</v>
       </c>
       <c r="B4" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>129851103</v>
       </c>
       <c r="B5" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129851087</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129851058</v>
       </c>
       <c r="B7" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>129851133</v>
       </c>
       <c r="B8" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>129851055</v>
       </c>
       <c r="B9" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25839-2025 artfynd.xlsx
+++ b/artfynd/A 25839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851102</v>
       </c>
       <c r="B2" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129851150</v>
       </c>
       <c r="B3" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129851149</v>
       </c>
       <c r="B4" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>129851103</v>
       </c>
       <c r="B5" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129851087</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129851058</v>
       </c>
       <c r="B7" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>129851133</v>
       </c>
       <c r="B8" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>129851055</v>
       </c>
       <c r="B9" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25839-2025 artfynd.xlsx
+++ b/artfynd/A 25839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851102</v>
       </c>
       <c r="B2" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129851150</v>
       </c>
       <c r="B3" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129851149</v>
       </c>
       <c r="B4" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>129851103</v>
       </c>
       <c r="B5" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129851087</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129851058</v>
       </c>
       <c r="B7" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>129851133</v>
       </c>
       <c r="B8" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>129851055</v>
       </c>
       <c r="B9" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25839-2025 artfynd.xlsx
+++ b/artfynd/A 25839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851102</v>
       </c>
       <c r="B2" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129851150</v>
       </c>
       <c r="B3" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129851149</v>
       </c>
       <c r="B4" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>129851103</v>
       </c>
       <c r="B5" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129851087</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129851058</v>
       </c>
       <c r="B7" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>129851133</v>
       </c>
       <c r="B8" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>129851055</v>
       </c>
       <c r="B9" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25839-2025 artfynd.xlsx
+++ b/artfynd/A 25839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851102</v>
       </c>
       <c r="B2" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129851150</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129851149</v>
       </c>
       <c r="B4" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>129851103</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129851087</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129851058</v>
       </c>
       <c r="B7" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>129851133</v>
       </c>
       <c r="B8" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>129851055</v>
       </c>
       <c r="B9" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25839-2025 artfynd.xlsx
+++ b/artfynd/A 25839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851102</v>
       </c>
       <c r="B2" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129851150</v>
       </c>
       <c r="B3" t="n">
-        <v>98832</v>
+        <v>98849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129851149</v>
       </c>
       <c r="B4" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>129851103</v>
       </c>
       <c r="B5" t="n">
-        <v>98832</v>
+        <v>98849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129851087</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129851058</v>
       </c>
       <c r="B7" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>129851133</v>
       </c>
       <c r="B8" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>129851055</v>
       </c>
       <c r="B9" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25839-2025 artfynd.xlsx
+++ b/artfynd/A 25839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851102</v>
       </c>
       <c r="B2" t="n">
-        <v>98748</v>
+        <v>98750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129851150</v>
       </c>
       <c r="B3" t="n">
-        <v>98865</v>
+        <v>98867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129851149</v>
       </c>
       <c r="B4" t="n">
-        <v>98748</v>
+        <v>98750</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>129851103</v>
       </c>
       <c r="B5" t="n">
-        <v>98865</v>
+        <v>98867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129851087</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129851058</v>
       </c>
       <c r="B7" t="n">
-        <v>98748</v>
+        <v>98750</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>129851133</v>
       </c>
       <c r="B8" t="n">
-        <v>98748</v>
+        <v>98750</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>129851055</v>
       </c>
       <c r="B9" t="n">
-        <v>98748</v>
+        <v>98750</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25839-2025 artfynd.xlsx
+++ b/artfynd/A 25839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851102</v>
       </c>
       <c r="B2" t="n">
-        <v>98750</v>
+        <v>98837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129851150</v>
       </c>
       <c r="B3" t="n">
-        <v>98867</v>
+        <v>98954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129851149</v>
       </c>
       <c r="B4" t="n">
-        <v>98750</v>
+        <v>98837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>129851103</v>
       </c>
       <c r="B5" t="n">
-        <v>98867</v>
+        <v>98954</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129851087</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129851058</v>
+        <v>129851133</v>
       </c>
       <c r="B7" t="n">
-        <v>98750</v>
+        <v>98837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>806697</v>
+        <v>806692</v>
       </c>
       <c r="R7" t="n">
-        <v>7324757</v>
+        <v>7324751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129851133</v>
+        <v>129851058</v>
       </c>
       <c r="B8" t="n">
-        <v>98750</v>
+        <v>98837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>806692</v>
+        <v>806697</v>
       </c>
       <c r="R8" t="n">
-        <v>7324751</v>
+        <v>7324757</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
         <v>129851055</v>
       </c>
       <c r="B9" t="n">
-        <v>98750</v>
+        <v>98837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
